--- a/Рыжов_Степан_Лаб1.xlsx
+++ b/Рыжов_Степан_Лаб1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\3-МД-20 ПИ\Рыжов Степан\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepanryzov/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844DCC68-5392-4621-AFBB-C12D5D97FDCA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D7CFFD-41D2-8E4D-99D6-550A5439086E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -63,95 +63,95 @@
     <t>Окружение</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows 10Pro Версия 10.0.19045 Сборка 19045, Google Chrome Версия: 140.0.7339.81
+    <t>Результат</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>YM002</t>
+  </si>
+  <si>
+    <t>YM003</t>
+  </si>
+  <si>
+    <t>YM004</t>
+  </si>
+  <si>
+    <t>YM005</t>
+  </si>
+  <si>
+    <t>YM006</t>
+  </si>
+  <si>
+    <t>YM007</t>
+  </si>
+  <si>
+    <t>Проверка работы кнопки "-" для уменьшения масштаба</t>
+  </si>
+  <si>
+    <t>YM008</t>
+  </si>
+  <si>
+    <t>Масштаб карты увеличен</t>
+  </si>
+  <si>
+    <t>Масштаб карты  увеличен</t>
+  </si>
+  <si>
+    <t>Проверка работы кнопки "+" для уменьшения масштаба</t>
+  </si>
+  <si>
+    <t>1.Нажать кнопку "+" в правой части экрана</t>
+  </si>
+  <si>
+    <t>1.Прокрутить "СКМ" вниз</t>
+  </si>
+  <si>
+    <t>1.Прокрутить "СКМ" вверх</t>
+  </si>
+  <si>
+    <t>Iphone 14 Pro IOS 26.6, Яндекс.Карты 30.6.2</t>
+  </si>
+  <si>
+    <t>1.Сведение двумя пальцами по экрану(Pinch)</t>
+  </si>
+  <si>
+    <t>1.Разведение двумя пальцами по экрану (Stretch)</t>
+  </si>
+  <si>
+    <t>1.Дважды нажать "ПКМ"</t>
+  </si>
+  <si>
+    <t>1.Дважды нажать "ЛКМ"</t>
+  </si>
+  <si>
+    <t>Проверка работы прокрутки "СКМ" вних для уменьшения масштаба</t>
+  </si>
+  <si>
+    <t>Провека работы двойного нажатия "ПКМ" для уменьшения масштаба</t>
+  </si>
+  <si>
+    <t>Проверка работы сенсора для уменьшение двумя пальцами</t>
+  </si>
+  <si>
+    <t>Проверка работы прокрутки "СКМ" вверх для уменьшения масштаба</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Провека работы двойного нажатия "ЛКМ" для уменьшения масштаба</t>
+  </si>
+  <si>
+    <t>Проверка работы сенсора для увеличение двумя пальцами</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows 11 Версия 25H2 Сборка 26200.9457, Яндекс Браузер Версия: 26.8.2.1064
 </t>
   </si>
   <si>
-    <t>Результат</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>YM002</t>
-  </si>
-  <si>
-    <t>YM003</t>
-  </si>
-  <si>
-    <t>YM004</t>
-  </si>
-  <si>
-    <t>YM005</t>
-  </si>
-  <si>
-    <t>YM006</t>
-  </si>
-  <si>
-    <t>YM007</t>
-  </si>
-  <si>
-    <t>Проверка работы кнопки "-" для уменьшения масштаба</t>
-  </si>
-  <si>
-    <t>YM008</t>
-  </si>
-  <si>
-    <t>Windows 10Pro Версия 10.0.19045 Сборка 19045, Google Chrome Версия: 140.0.7339.81</t>
-  </si>
-  <si>
-    <t>Масштаб карты увеличен</t>
-  </si>
-  <si>
-    <t>Масштаб карты  увеличен</t>
-  </si>
-  <si>
-    <t>Проверка работы кнопки "+" для уменьшения масштаба</t>
-  </si>
-  <si>
-    <t>1.Нажать кнопку "+" в правой части экрана</t>
-  </si>
-  <si>
-    <t>"СКМ" вних</t>
-  </si>
-  <si>
-    <t>"СКМ" вверх</t>
-  </si>
-  <si>
-    <t>Двойное нажатие "ПКМ"</t>
-  </si>
-  <si>
-    <t>Двойное нажатие "ЛКМ"</t>
-  </si>
-  <si>
-    <t>1.Прокрутить "СКМ" вниз</t>
-  </si>
-  <si>
-    <t>1.Прокрутить "СКМ" вверх</t>
-  </si>
-  <si>
-    <t>1.Два раза нажать "ПКМ"</t>
-  </si>
-  <si>
-    <t>1.Два раза нажать "ЛКМ"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Открыть   Яндекс.Карты </t>
-  </si>
-  <si>
-    <t>Iphone 14 Pro IOS 26.6, Яндекс.Карты 30.6.2</t>
-  </si>
-  <si>
-    <t>Уменьшение двумя пальцами</t>
-  </si>
-  <si>
-    <t>Увеличение двумя пальцами</t>
-  </si>
-  <si>
-    <t>1.Сведение двумя пальцами по экрану(Pinch)</t>
-  </si>
-  <si>
-    <t>1.Разведение двумя пальцами по экрану (Stretch)</t>
+    <t>Windows 11 Версия 25H2 Сборка 26200.9457, Яндекс Браузер Версия: 26.8.2.1064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Открыть   Яндекс.Карты Версия: 30.2.1 (337327) </t>
   </si>
 </sst>
 </file>
@@ -477,20 +477,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="20.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="1"/>
+    <col min="3" max="3" width="20.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" customWidth="1"/>
     <col min="9" max="9" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,10 +516,10 @@
         <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -527,7 +527,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
@@ -542,27 +542,27 @@
         <v>10</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
@@ -571,27 +571,27 @@
         <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
@@ -600,27 +600,27 @@
         <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
@@ -629,126 +629,126 @@
         <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
